--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E517"/>
+  <dimension ref="A1:E522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11287,6 +11287,111 @@
         <v>437.48</v>
       </c>
       <c r="E517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>376.34</v>
+      </c>
+      <c r="C518" t="n">
+        <v>371.95</v>
+      </c>
+      <c r="D518" t="n">
+        <v>438.11</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>376.93</v>
+      </c>
+      <c r="C519" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="D519" t="n">
+        <v>438.62</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="C520" t="n">
+        <v>373.97</v>
+      </c>
+      <c r="D520" t="n">
+        <v>439.5</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="C521" t="n">
+        <v>374.48</v>
+      </c>
+      <c r="D521" t="n">
+        <v>440.2</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>378.37</v>
+      </c>
+      <c r="C522" t="n">
+        <v>374.68</v>
+      </c>
+      <c r="D522" t="n">
+        <v>440.1</v>
+      </c>
+      <c r="E522" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11303,7 +11408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B592"/>
+  <dimension ref="A1:B597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17226,6 +17331,56 @@
       </c>
       <c r="B592" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -17394,28 +17549,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06280992485312313</v>
+        <v>-0.06128992058734824</v>
       </c>
       <c r="J2" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02436658267990355</v>
+        <v>0.0236587905678084</v>
       </c>
       <c r="M2" t="n">
-        <v>2.392756662367463</v>
+        <v>2.378545082614268</v>
       </c>
       <c r="N2" t="n">
-        <v>9.455023695731761</v>
+        <v>9.376482083470199</v>
       </c>
       <c r="O2" t="n">
-        <v>3.074902225393803</v>
+        <v>3.062104192131646</v>
       </c>
       <c r="P2" t="n">
-        <v>378.328980314225</v>
+        <v>378.3132432691153</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17472,28 +17627,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1262360935464619</v>
+        <v>-0.127169880029999</v>
       </c>
       <c r="J3" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="K3" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07000772643256159</v>
+        <v>0.07223913969647233</v>
       </c>
       <c r="M3" t="n">
-        <v>2.712582531167317</v>
+        <v>2.695858731117361</v>
       </c>
       <c r="N3" t="n">
-        <v>12.648772561989</v>
+        <v>12.54100400826293</v>
       </c>
       <c r="O3" t="n">
-        <v>3.556511290856391</v>
+        <v>3.541328000660618</v>
       </c>
       <c r="P3" t="n">
-        <v>377.4707823221131</v>
+        <v>377.4804367933829</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17550,28 +17705,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008874690297708035</v>
+        <v>-0.01053531502634061</v>
       </c>
       <c r="J4" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="K4" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004569306690581643</v>
+        <v>0.0006559444118569013</v>
       </c>
       <c r="M4" t="n">
-        <v>2.480731071353565</v>
+        <v>2.466601111649041</v>
       </c>
       <c r="N4" t="n">
-        <v>10.29450668165298</v>
+        <v>10.21041399728333</v>
       </c>
       <c r="O4" t="n">
-        <v>3.20850536568867</v>
+        <v>3.195373843118099</v>
       </c>
       <c r="P4" t="n">
-        <v>440.4839492108271</v>
+        <v>440.5011327588844</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17609,7 +17764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E517"/>
+  <dimension ref="A1:E522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31567,6 +31722,141 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-35.018257208734155,173.85920806059832</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-35.01886844898497,173.859677559137</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-35.018757378475854,173.86080033992027</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-35.01825410890021,173.8592133159565</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-35.018863955255284,173.8596827894428</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-35.01875352253784,173.86080338567618</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-35.01824990573519,173.85922044186526</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-35.01885529342787,173.85969287104504</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-35.01874686915445,173.86080864109738</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-35.01824790923167,173.85922382667167</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-35.018851971975046,173.85969673692205</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-35.01874157669022,173.86081282154547</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-35.01824654320289,173.85922614259175</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-35.01885066944448,173.85969825295217</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-35.01874233275653,173.86081222433862</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E522"/>
+  <dimension ref="A1:E525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11394,6 +11394,69 @@
       <c r="E522" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="C523" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="D523" t="n">
+        <v>440.58</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="C524" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="D524" t="n">
+        <v>441.11</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="C525" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="D525" t="n">
+        <v>441.27</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11408,7 +11471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B597"/>
+  <dimension ref="A1:B600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17381,6 +17444,36 @@
       </c>
       <c r="B597" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -17549,28 +17642,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06128992058734824</v>
+        <v>-0.05873752320268373</v>
       </c>
       <c r="J2" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K2" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0236587905678084</v>
+        <v>0.02194635967544278</v>
       </c>
       <c r="M2" t="n">
-        <v>2.378545082614268</v>
+        <v>2.377760679711022</v>
       </c>
       <c r="N2" t="n">
-        <v>9.376482083470199</v>
+        <v>9.356687114214818</v>
       </c>
       <c r="O2" t="n">
-        <v>3.062104192131646</v>
+        <v>3.058870234942113</v>
       </c>
       <c r="P2" t="n">
-        <v>378.3132432691153</v>
+        <v>378.2867540415089</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17627,28 +17720,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.127169880029999</v>
+        <v>-0.1256383047201126</v>
       </c>
       <c r="J3" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07223913969647233</v>
+        <v>0.07134559842381727</v>
       </c>
       <c r="M3" t="n">
-        <v>2.695858731117361</v>
+        <v>2.688116545827459</v>
       </c>
       <c r="N3" t="n">
-        <v>12.54100400826293</v>
+        <v>12.48180668672139</v>
       </c>
       <c r="O3" t="n">
-        <v>3.541328000660618</v>
+        <v>3.532960046012605</v>
       </c>
       <c r="P3" t="n">
-        <v>377.4804367933829</v>
+        <v>377.464529962625</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17705,28 +17798,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01053531502634061</v>
+        <v>-0.009725290240661355</v>
       </c>
       <c r="J4" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K4" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006559444118569013</v>
+        <v>0.0005654468635933885</v>
       </c>
       <c r="M4" t="n">
-        <v>2.466601111649041</v>
+        <v>2.456495787328641</v>
       </c>
       <c r="N4" t="n">
-        <v>10.21041399728333</v>
+        <v>10.15579868348046</v>
       </c>
       <c r="O4" t="n">
-        <v>3.195373843118099</v>
+        <v>3.18681638684761</v>
       </c>
       <c r="P4" t="n">
-        <v>440.5011327588844</v>
+        <v>440.4927192230928</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17764,7 +17857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E522"/>
+  <dimension ref="A1:E525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31857,6 +31950,87 @@
         </is>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-35.01824522971363,173.85922836943791</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-35.01884812950986,173.85970120921075</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-35.018738703638135,173.86081509093134</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-35.01824202479966,173.85923380294224</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-35.01884487318329,173.85970499928558</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-35.018734696486504,173.86081825612717</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-35.01824097400816,173.85923558441897</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-35.018842854260775,173.8597073491318</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-35.018733486780334,173.86081921165794</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E525"/>
+  <dimension ref="A1:E528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11457,6 +11457,69 @@
       <c r="E525" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="C526" t="n">
+        <v>376.62</v>
+      </c>
+      <c r="D526" t="n">
+        <v>442.26</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="C527" t="n">
+        <v>376.78</v>
+      </c>
+      <c r="D527" t="n">
+        <v>442.1</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>379.84</v>
+      </c>
+      <c r="C528" t="n">
+        <v>376.99</v>
+      </c>
+      <c r="D528" t="n">
+        <v>442.41</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17474,6 +17537,36 @@
       </c>
       <c r="B600" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -17642,28 +17735,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05873752320268373</v>
+        <v>-0.05553099867497165</v>
       </c>
       <c r="J2" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02194635967544278</v>
+        <v>0.01977826378063774</v>
       </c>
       <c r="M2" t="n">
-        <v>2.377760679711022</v>
+        <v>2.380634098642136</v>
       </c>
       <c r="N2" t="n">
-        <v>9.356687114214818</v>
+        <v>9.356595346385799</v>
       </c>
       <c r="O2" t="n">
-        <v>3.058870234942113</v>
+        <v>3.058855234623862</v>
       </c>
       <c r="P2" t="n">
-        <v>378.2867540415089</v>
+        <v>378.2533307184211</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17720,28 +17813,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1256383047201126</v>
+        <v>-0.1227955613312456</v>
       </c>
       <c r="J3" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07134559842381727</v>
+        <v>0.06890823608462104</v>
       </c>
       <c r="M3" t="n">
-        <v>2.688116545827459</v>
+        <v>2.687094826185951</v>
       </c>
       <c r="N3" t="n">
-        <v>12.48180668672139</v>
+        <v>12.45263391601879</v>
       </c>
       <c r="O3" t="n">
-        <v>3.532960046012605</v>
+        <v>3.528828972338953</v>
       </c>
       <c r="P3" t="n">
-        <v>377.464529962625</v>
+        <v>377.4348775155448</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17798,28 +17891,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.009725290240661355</v>
+        <v>-0.007616675754492942</v>
       </c>
       <c r="J4" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K4" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005654468635933885</v>
+        <v>0.0003502095073822931</v>
       </c>
       <c r="M4" t="n">
-        <v>2.456495787328641</v>
+        <v>2.45284771750153</v>
       </c>
       <c r="N4" t="n">
-        <v>10.15579868348046</v>
+        <v>10.12104636383948</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18681638684761</v>
+        <v>3.18135920069386</v>
       </c>
       <c r="P4" t="n">
-        <v>440.4927192230928</v>
+        <v>440.4707244154801</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17857,7 +17950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E525"/>
+  <dimension ref="A1:E528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32031,6 +32124,87 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-35.01823892496464,173.85923905829847</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-35.01883803489714,173.85971295844175</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-35.01872600172324,173.86082512400387</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-35.01823966051873,173.85923781126482</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-35.01883699287253,173.85971417126544</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-35.01872721142944,173.8608241684733</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-35.018238819885475,173.85923923644614</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-35.01883562521524,173.85971576309646</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-35.018724867623646,173.86082601981377</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
